--- a/Testes/reescala/Teste populacao e gerações/Teste3/1_populacao_final.xlsx
+++ b/Testes/reescala/Teste populacao e gerações/Teste3/1_populacao_final.xlsx
@@ -2719,8 +2719,8 @@
       <c r="P19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="5" t="n">
-        <v>0</v>
+      <c r="Q19" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>0</v>
@@ -3342,11 +3342,11 @@
       <c r="AF24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="4" t="n">
-        <v>1</v>
+      <c r="AG24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI24" s="5" t="n">
         <v>0</v>
@@ -3639,8 +3639,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -3678,8 +3678,8 @@
       <c r="AC27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" s="5" t="n">
-        <v>0</v>
+      <c r="AD27" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AE27" s="5" t="n">
         <v>0</v>
@@ -4692,8 +4692,8 @@
       <c r="V36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="5" t="n">
-        <v>0</v>
+      <c r="W36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="X36" s="5" t="n">
         <v>0</v>
@@ -4722,11 +4722,11 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>0</v>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI36" s="5" t="n">
         <v>0</v>
@@ -9080,8 +9080,8 @@
       <c r="P19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="5" t="n">
-        <v>0</v>
+      <c r="Q19" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>0</v>
@@ -9703,11 +9703,11 @@
       <c r="AF24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="4" t="n">
-        <v>1</v>
+      <c r="AG24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI24" s="5" t="n">
         <v>0</v>
@@ -10000,8 +10000,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -11083,11 +11083,11 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>0</v>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI36" s="5" t="n">
         <v>0</v>
@@ -15441,8 +15441,8 @@
       <c r="P19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="5" t="n">
-        <v>0</v>
+      <c r="Q19" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>0</v>
@@ -16064,11 +16064,11 @@
       <c r="AF24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="4" t="n">
-        <v>1</v>
+      <c r="AG24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI24" s="5" t="n">
         <v>0</v>
@@ -16361,8 +16361,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -17414,8 +17414,8 @@
       <c r="V36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="5" t="n">
-        <v>0</v>
+      <c r="W36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="X36" s="5" t="n">
         <v>0</v>
@@ -17444,11 +17444,11 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>0</v>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI36" s="5" t="n">
         <v>0</v>
@@ -21802,8 +21802,8 @@
       <c r="P19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="5" t="n">
-        <v>0</v>
+      <c r="Q19" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>0</v>
@@ -22425,11 +22425,11 @@
       <c r="AF24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="4" t="n">
-        <v>1</v>
+      <c r="AG24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI24" s="5" t="n">
         <v>0</v>
@@ -22722,8 +22722,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -23805,11 +23805,11 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>0</v>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI36" s="5" t="n">
         <v>0</v>
@@ -28163,8 +28163,8 @@
       <c r="P19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="5" t="n">
-        <v>0</v>
+      <c r="Q19" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>0</v>
@@ -28786,11 +28786,11 @@
       <c r="AF24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="4" t="n">
-        <v>1</v>
+      <c r="AG24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI24" s="5" t="n">
         <v>0</v>
@@ -29083,8 +29083,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -30136,8 +30136,8 @@
       <c r="V36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="5" t="n">
-        <v>0</v>
+      <c r="W36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="X36" s="5" t="n">
         <v>0</v>
@@ -30166,11 +30166,11 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>0</v>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI36" s="5" t="n">
         <v>0</v>
@@ -34524,8 +34524,8 @@
       <c r="P19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="5" t="n">
-        <v>0</v>
+      <c r="Q19" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>0</v>
@@ -35147,11 +35147,11 @@
       <c r="AF24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="4" t="n">
-        <v>1</v>
+      <c r="AG24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI24" s="5" t="n">
         <v>0</v>
@@ -35444,8 +35444,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -35483,8 +35483,8 @@
       <c r="AC27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" s="5" t="n">
-        <v>0</v>
+      <c r="AD27" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AE27" s="5" t="n">
         <v>0</v>
@@ -36527,11 +36527,11 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>0</v>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI36" s="5" t="n">
         <v>0</v>
@@ -40885,8 +40885,8 @@
       <c r="P19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="5" t="n">
-        <v>0</v>
+      <c r="Q19" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>0</v>
@@ -41508,11 +41508,11 @@
       <c r="AF24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="4" t="n">
-        <v>1</v>
+      <c r="AG24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI24" s="5" t="n">
         <v>0</v>
@@ -41805,8 +41805,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -42888,11 +42888,11 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>0</v>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI36" s="5" t="n">
         <v>0</v>
@@ -44250,11 +44250,11 @@
       <c r="Z48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AA48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" s="4" t="n">
-        <v>1</v>
+      <c r="AA48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB48" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AC48" s="5" t="n">
         <v>0</v>
@@ -47246,8 +47246,8 @@
       <c r="P19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="5" t="n">
-        <v>0</v>
+      <c r="Q19" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>0</v>
@@ -47869,11 +47869,11 @@
       <c r="AF24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="4" t="n">
-        <v>1</v>
+      <c r="AG24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI24" s="5" t="n">
         <v>0</v>
@@ -48166,8 +48166,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -48205,8 +48205,8 @@
       <c r="AC27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" s="5" t="n">
-        <v>0</v>
+      <c r="AD27" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AE27" s="5" t="n">
         <v>0</v>
@@ -49219,8 +49219,8 @@
       <c r="V36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="5" t="n">
-        <v>0</v>
+      <c r="W36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="X36" s="5" t="n">
         <v>0</v>
@@ -49249,11 +49249,11 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>0</v>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI36" s="5" t="n">
         <v>0</v>
@@ -53607,8 +53607,8 @@
       <c r="P19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="5" t="n">
-        <v>0</v>
+      <c r="Q19" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>0</v>
@@ -54230,11 +54230,11 @@
       <c r="AF24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="4" t="n">
-        <v>1</v>
+      <c r="AG24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI24" s="5" t="n">
         <v>0</v>
@@ -54527,8 +54527,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -54566,8 +54566,8 @@
       <c r="AC27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" s="5" t="n">
-        <v>0</v>
+      <c r="AD27" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AE27" s="5" t="n">
         <v>0</v>
@@ -55580,8 +55580,8 @@
       <c r="V36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="5" t="n">
-        <v>0</v>
+      <c r="W36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="X36" s="5" t="n">
         <v>0</v>
@@ -55610,11 +55610,11 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>0</v>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI36" s="5" t="n">
         <v>0</v>
@@ -59968,8 +59968,8 @@
       <c r="P19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="5" t="n">
-        <v>0</v>
+      <c r="Q19" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>0</v>
@@ -60591,11 +60591,11 @@
       <c r="AF24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="4" t="n">
-        <v>1</v>
+      <c r="AG24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI24" s="5" t="n">
         <v>0</v>
@@ -60888,8 +60888,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -60927,8 +60927,8 @@
       <c r="AC27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" s="5" t="n">
-        <v>0</v>
+      <c r="AD27" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AE27" s="5" t="n">
         <v>0</v>
@@ -61941,8 +61941,8 @@
       <c r="V36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="5" t="n">
-        <v>0</v>
+      <c r="W36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="X36" s="5" t="n">
         <v>0</v>
@@ -61971,11 +61971,11 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>0</v>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI36" s="5" t="n">
         <v>0</v>
@@ -62967,11 +62967,11 @@
       <c r="S45" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U45" s="5" t="n">
-        <v>0</v>
+      <c r="T45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="V45" s="5" t="n">
         <v>0</v>
@@ -63333,11 +63333,11 @@
       <c r="Z48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AA48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" s="4" t="n">
-        <v>1</v>
+      <c r="AA48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB48" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AC48" s="5" t="n">
         <v>0</v>
@@ -63654,8 +63654,8 @@
       <c r="R51" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S51" s="4" t="n">
-        <v>1</v>
+      <c r="S51" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="T51" s="5" t="n">
         <v>0</v>
